--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,643 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121551328</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97045</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rörtjärn, SV om, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>303175</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6453772</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tegneby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander, Jonny Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121551340</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97045</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rörtjärn, SV om, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>303115</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6453709</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tegneby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander, Jonny Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121551342</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97045</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rörtjärn, SV om, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>303068</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6453664</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tegneby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander, Jonny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121551357</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92025</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rörtjärn, SV om, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>302946</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6453501</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tegneby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander, Jonny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121551355</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97046</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6052779</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grön groddlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>302452</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6452822</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tegneby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander, Jonny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121551316</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97055</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rörtjärn, SV om, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>303098</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6453670</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tegneby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander, Jonny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551328</v>
+        <v>121551340</v>
       </c>
       <c r="B3" t="n">
-        <v>97045</v>
+        <v>97050</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>303175</v>
+        <v>303115</v>
       </c>
       <c r="R3" t="n">
-        <v>6453772</v>
+        <v>6453709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551340</v>
+        <v>121551328</v>
       </c>
       <c r="B4" t="n">
-        <v>97045</v>
+        <v>97050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>303115</v>
+        <v>303175</v>
       </c>
       <c r="R4" t="n">
-        <v>6453709</v>
+        <v>6453772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551342</v>
+        <v>121551355</v>
       </c>
       <c r="B5" t="n">
-        <v>97045</v>
+        <v>97051</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224361</v>
+        <v>6052779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,14 +1061,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>303068</v>
+        <v>302452</v>
       </c>
       <c r="R5" t="n">
-        <v>6453664</v>
+        <v>6452822</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121551357</v>
+        <v>121551316</v>
       </c>
       <c r="B6" t="n">
-        <v>92025</v>
+        <v>97060</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,30 +1140,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>224363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>302946</v>
+        <v>303098</v>
       </c>
       <c r="R6" t="n">
-        <v>6453501</v>
+        <v>6453670</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121551355</v>
+        <v>121551342</v>
       </c>
       <c r="B7" t="n">
-        <v>97046</v>
+        <v>97050</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6052779</v>
+        <v>224361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,14 +1271,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>302452</v>
+        <v>303068</v>
       </c>
       <c r="R7" t="n">
-        <v>6452822</v>
+        <v>6453664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121551316</v>
+        <v>121551357</v>
       </c>
       <c r="B8" t="n">
-        <v>97055</v>
+        <v>92030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,27 +1350,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224363</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>303098</v>
+        <v>302946</v>
       </c>
       <c r="R8" t="n">
-        <v>6453670</v>
+        <v>6453501</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>121551340</v>
       </c>
       <c r="B3" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>121551328</v>
       </c>
       <c r="B4" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551355</v>
+        <v>121551316</v>
       </c>
       <c r="B5" t="n">
-        <v>97051</v>
+        <v>97061</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,23 +1037,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6052779</v>
+        <v>224363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -1061,17 +1057,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>302452</v>
+        <v>303098</v>
       </c>
       <c r="R5" t="n">
-        <v>6452822</v>
+        <v>6453670</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121551316</v>
+        <v>121551355</v>
       </c>
       <c r="B6" t="n">
-        <v>97060</v>
+        <v>97052</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,19 +1140,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>6052779</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1164,17 +1164,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>303098</v>
+        <v>302452</v>
       </c>
       <c r="R6" t="n">
-        <v>6453670</v>
+        <v>6452822</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>121551342</v>
       </c>
       <c r="B7" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>121551357</v>
       </c>
       <c r="B8" t="n">
-        <v>92030</v>
+        <v>92031</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551340</v>
+        <v>121551355</v>
       </c>
       <c r="B3" t="n">
-        <v>97051</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224361</v>
+        <v>6052779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,14 +847,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>303115</v>
+        <v>302452</v>
       </c>
       <c r="R3" t="n">
-        <v>6453709</v>
+        <v>6452822</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551328</v>
+        <v>121551316</v>
       </c>
       <c r="B4" t="n">
-        <v>97051</v>
+        <v>97061</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,23 +930,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224361</v>
+        <v>224363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -958,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>303175</v>
+        <v>303098</v>
       </c>
       <c r="R4" t="n">
-        <v>6453772</v>
+        <v>6453670</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551316</v>
+        <v>121551357</v>
       </c>
       <c r="B5" t="n">
-        <v>97061</v>
+        <v>92031</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,27 +1029,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224363</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>303098</v>
+        <v>302946</v>
       </c>
       <c r="R5" t="n">
-        <v>6453670</v>
+        <v>6453501</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121551355</v>
+        <v>121551340</v>
       </c>
       <c r="B6" t="n">
-        <v>97052</v>
+        <v>97051</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6052779</v>
+        <v>224361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,14 +1163,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>302452</v>
+        <v>303115</v>
       </c>
       <c r="R6" t="n">
-        <v>6452822</v>
+        <v>6453709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1338,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121551357</v>
+        <v>121551328</v>
       </c>
       <c r="B8" t="n">
-        <v>92031</v>
+        <v>97051</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,30 +1349,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>224361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>302946</v>
+        <v>303175</v>
       </c>
       <c r="R8" t="n">
-        <v>6453501</v>
+        <v>6453772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551355</v>
+        <v>121551357</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>92031</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,42 +819,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6052779</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>302452</v>
+        <v>302946</v>
       </c>
       <c r="R3" t="n">
-        <v>6452822</v>
+        <v>6453501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1017,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551357</v>
+        <v>121551328</v>
       </c>
       <c r="B5" t="n">
-        <v>92031</v>
+        <v>97051</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,30 +1028,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>224361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>302946</v>
+        <v>303175</v>
       </c>
       <c r="R5" t="n">
-        <v>6453501</v>
+        <v>6453772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121551328</v>
+        <v>121551355</v>
       </c>
       <c r="B8" t="n">
-        <v>97051</v>
+        <v>97052</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>6052779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,14 +1377,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>303175</v>
+        <v>302452</v>
       </c>
       <c r="R8" t="n">
-        <v>6453772</v>
+        <v>6452822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551328</v>
+        <v>121551340</v>
       </c>
       <c r="B5" t="n">
         <v>97051</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>303175</v>
+        <v>303115</v>
       </c>
       <c r="R5" t="n">
-        <v>6453772</v>
+        <v>6453709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121551340</v>
+        <v>121551355</v>
       </c>
       <c r="B6" t="n">
-        <v>97051</v>
+        <v>97052</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224361</v>
+        <v>6052779</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,14 +1163,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>303115</v>
+        <v>302452</v>
       </c>
       <c r="R6" t="n">
-        <v>6453709</v>
+        <v>6452822</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121551355</v>
+        <v>121551328</v>
       </c>
       <c r="B8" t="n">
-        <v>97052</v>
+        <v>97051</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6052779</v>
+        <v>224361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,14 +1377,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>302452</v>
+        <v>303175</v>
       </c>
       <c r="R8" t="n">
-        <v>6452822</v>
+        <v>6453772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551357</v>
+        <v>121551342</v>
       </c>
       <c r="B3" t="n">
-        <v>92031</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,30 +819,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>224361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>302946</v>
+        <v>303068</v>
       </c>
       <c r="R3" t="n">
-        <v>6453501</v>
+        <v>6453664</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551316</v>
+        <v>121551340</v>
       </c>
       <c r="B4" t="n">
-        <v>97061</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,19 +930,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224363</v>
+        <v>224361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -953,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>303098</v>
+        <v>303115</v>
       </c>
       <c r="R4" t="n">
-        <v>6453670</v>
+        <v>6453709</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551340</v>
+        <v>121551328</v>
       </c>
       <c r="B5" t="n">
-        <v>97051</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>303115</v>
+        <v>303175</v>
       </c>
       <c r="R5" t="n">
-        <v>6453709</v>
+        <v>6453772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121551355</v>
+        <v>121551316</v>
       </c>
       <c r="B6" t="n">
-        <v>97052</v>
+        <v>97069</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,23 +1144,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6052779</v>
+        <v>224363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1163,17 +1164,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>302452</v>
+        <v>303098</v>
       </c>
       <c r="R6" t="n">
-        <v>6452822</v>
+        <v>6453670</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121551342</v>
+        <v>121551357</v>
       </c>
       <c r="B7" t="n">
-        <v>97051</v>
+        <v>92039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,31 +1243,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224361</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>303068</v>
+        <v>302946</v>
       </c>
       <c r="R7" t="n">
-        <v>6453664</v>
+        <v>6453501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121551328</v>
+        <v>121551355</v>
       </c>
       <c r="B8" t="n">
-        <v>97051</v>
+        <v>97060</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>6052779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,14 +1377,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>303175</v>
+        <v>302452</v>
       </c>
       <c r="R8" t="n">
-        <v>6453772</v>
+        <v>6452822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551328</v>
+        <v>121551355</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>97060</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224361</v>
+        <v>6052779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,14 +954,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>303175</v>
+        <v>302452</v>
       </c>
       <c r="R4" t="n">
-        <v>6453772</v>
+        <v>6452822</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551355</v>
+        <v>121551357</v>
       </c>
       <c r="B5" t="n">
-        <v>97060</v>
+        <v>92039</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,42 +1033,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6052779</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>302452</v>
+        <v>302946</v>
       </c>
       <c r="R5" t="n">
-        <v>6452822</v>
+        <v>6453501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1338,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121551357</v>
+        <v>121551328</v>
       </c>
       <c r="B8" t="n">
-        <v>92039</v>
+        <v>97059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,30 +1349,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>224361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>302946</v>
+        <v>303175</v>
       </c>
       <c r="R8" t="n">
-        <v>6453501</v>
+        <v>6453772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551342</v>
+        <v>121551316</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>97069</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,23 +823,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224361</v>
+        <v>224363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -851,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>303068</v>
+        <v>303098</v>
       </c>
       <c r="R3" t="n">
-        <v>6453664</v>
+        <v>6453670</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -914,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551355</v>
+        <v>121551328</v>
       </c>
       <c r="B4" t="n">
-        <v>97060</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6052779</v>
+        <v>224361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,14 +950,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>302452</v>
+        <v>303175</v>
       </c>
       <c r="R4" t="n">
-        <v>6452822</v>
+        <v>6453772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551357</v>
+        <v>121551340</v>
       </c>
       <c r="B5" t="n">
-        <v>92039</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,30 +1029,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>224361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>302946</v>
+        <v>303115</v>
       </c>
       <c r="R5" t="n">
-        <v>6453501</v>
+        <v>6453709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121551316</v>
+        <v>121551357</v>
       </c>
       <c r="B6" t="n">
-        <v>97069</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,27 +1136,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>303098</v>
+        <v>302946</v>
       </c>
       <c r="R6" t="n">
-        <v>6453670</v>
+        <v>6453501</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121551340</v>
+        <v>121551342</v>
       </c>
       <c r="B7" t="n">
         <v>97059</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>303115</v>
+        <v>303068</v>
       </c>
       <c r="R7" t="n">
-        <v>6453709</v>
+        <v>6453664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121551328</v>
+        <v>121551355</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>97060</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>6052779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grön groddlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,14 +1377,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Rörtjärn, SV om, vid vindkraftverk, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>303175</v>
+        <v>302452</v>
       </c>
       <c r="R8" t="n">
-        <v>6453772</v>
+        <v>6452822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -675,65 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68273483</v>
+        <v>121551357</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalsänka ca 200 m SV om Rörtjärn, Boh</t>
+          <t>Rörtjärn, SV om, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>303177.6869592609</v>
+        <v>302946</v>
       </c>
       <c r="R2" t="n">
-        <v>6453748.800691013</v>
+        <v>6453501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tidigare känt fynd från inventeringen av Bohusläns flora</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,18 +757,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonny Andersson</t>
+          <t>Tore Mattsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonny Andersson</t>
+          <t>Tore Mattsson, Olle Molander, Jonny Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -810,12 +779,7 @@
         <v>121551340</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,12 +881,7 @@
         <v>121551342</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551328</v>
+        <v>121551316</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,23 +991,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224361</v>
+        <v>224363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -1065,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>303175</v>
+        <v>303098</v>
       </c>
       <c r="R5" t="n">
-        <v>6453772</v>
+        <v>6453670</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,53 +1078,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121551357</v>
+        <v>68273483</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörtjärn, SV om, Boh</t>
+          <t>Dalsänka ca 200 m SV om Rörtjärn, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>302946</v>
+        <v>303178</v>
       </c>
       <c r="R6" t="n">
-        <v>6453501</v>
+        <v>6453749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,12 +1158,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2017-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2017-07-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tidigare känt fynd från inventeringen av Bohusläns flora</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,34 +1177,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tore Mattsson</t>
+          <t>Jonny Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tore Mattsson, Olle Molander, Jonny Andersson</t>
+          <t>Jonny Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121551316</v>
+        <v>121551328</v>
       </c>
       <c r="B7" t="n">
-        <v>97069</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,19 +1206,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224363</v>
+        <v>224361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1274,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>303098</v>
+        <v>303175</v>
       </c>
       <c r="R7" t="n">
-        <v>6453670</v>
+        <v>6453772</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 49930-2024 artfynd.xlsx
+++ b/artfynd/A 49930-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121551357</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273483</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121551328</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121551340</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121551342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,8 +1324,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121551316</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>